--- a/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,7 +1101,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1123,42 +1123,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
@@ -573,51 +573,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KV57ZPHB45GVJ88EC0APPFJJ</t>
+          <t>h_01KVFFE8SV63QAKTX4P4GQWD4P</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV57ZPHB45GVJ88EC0APPFJJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVFFE8SV63QAKTX4P4GQWD4P</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HCM Bridge</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KVFE5DW0W0ZQY6YSACJXK5P5</t>
+          <t>h_01KVFE13Y155MAF3FSDZDFMK28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVFE5DW0W0ZQY6YSACJXK5P5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVFE13Y155MAF3FSDZDFMK28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Service Desk Bridge</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KVFTD727XBN9SJBB1VR4YKQT</t>
+          <t>h_01KV58G6P4PZDG5K1M2ZYZMAF9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVFTD727XBN9SJBB1VR4YKQT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV58G6P4PZDG5K1M2ZYZMAF9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Filter Employees</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,41 +649,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KVFFE8SV63QAKTX4P4GQWD4P</t>
+          <t>h_01KW99TXRPDSKSKEW8YJCQGTNN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVFFE8SV63QAKTX4P4GQWD4P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KW99TXRPDSKSKEW8YJCQGTNN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Employee Filter Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KVFE13Y155MAF3FSDZDFMK28</t>
+          <t>h_01KW9CC09AMV3E6K7G5X78EPEV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVFE13Y155MAF3FSDZDFMK28</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KW9CC09AMV3E6K7G5X78EPEV</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Filter Candidates</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KV58G6P4PZDG5K1M2ZYZMAF9</t>
+          <t>h_01KXDDRMW362G65D2D6KHSPNDV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV58G6P4PZDG5K1M2ZYZMAF9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KXDDRMW362G65D2D6KHSPNDV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Source Application</t>
+          <t>Candidate Filter Configuration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,85 +715,85 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KVQ19PSN053M4K6ZBGXQRM1F</t>
+          <t>h_01KXDDYHXYA3GAYMBVCQJ84037</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVQ19PSN053M4K6ZBGXQRM1F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KXDDYHXYA3GAYMBVCQJ84037</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Source Configuration</t>
+          <t>Service Desk</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KVFTD7271CM4SG6359SM3ACP</t>
+          <t>h_01KV580JN6Y6WH1M2HDGY6JTWB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVFTD7271CM4SG6359SM3ACP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV580JN6Y6WH1M2HDGY6JTWB</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Service Desk</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KV580JN6Y6WH1M2HDGY6JTWB</t>
+          <t>h_01KV5AWNTPZPYF77BM6DAABDME</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV580JN6Y6WH1M2HDGY6JTWB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV5AWNTPZPYF77BM6DAABDME</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>ITSM Configuration</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KV5AWNTPZPYF77BM6DAABDME</t>
+          <t>h_01KYVN45H4W8G06FVKZT2P3R5Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV5AWNTPZPYF77BM6DAABDME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KYVN45H4W8G06FVKZT2P3R5Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Target Application</t>
+          <t>Messaging Application Configuration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,195 +803,195 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KVPZZE2GTMRJTXMG1YHMT063</t>
+          <t>h_01KYW0Q7528S0P5VAQBVPK62R2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVPZZE2GTMRJTXMG1YHMT063</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KYW0Q7528S0P5VAQBVPK62R2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Application</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KVPYYB9H42QYMRTRRZC4S7X4</t>
+          <t>h_01KV5DGBF812MM5BKGE37A93MK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVPYYB9H42QYMRTRRZC4S7X4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV5DGBF812MM5BKGE37A93MK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lifecycle Event</t>
+          <t>Event Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KV5DGBF812MM5BKGE37A93MK</t>
+          <t>h_01KV5M76XT6PD9SQD744GWQ7T7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV5DGBF812MM5BKGE37A93MK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV5M76XT6PD9SQD744GWQ7T7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Event Configuration</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KV5M76XT6PD9SQD744GWQ7T7</t>
+          <t>h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV5M76XT6PD9SQD744GWQ7T7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KV580PQB96710J73V3BG96A9</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV580PQB96710J73V3BG96A9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Notification Delivery Channel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Delivery Channel</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,85 +1023,85 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,41 +1111,41 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>

--- a/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Event Configuration</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">

--- a/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Delivery Channel</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7VV1J9X30QVYDJQDGBQMRQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,151 +979,151 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,54 +1133,10 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Operation safeguard settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,41 +1023,41 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>h_01KZZD8D8R71K9E8M25TMARJG8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KZZD8D8R71K9E8M25TMARJG8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,41 +1067,41 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,32 +1111,54 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-ServiceNow-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
